--- a/weekly_sample_output.xlsx
+++ b/weekly_sample_output.xlsx
@@ -11,6 +11,9 @@
     <sheet name="Agency Employee" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Gazebo Employee" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Analysis" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="EMP Agency Total" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Category summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Hours over 60" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K191"/>
+  <dimension ref="A1:K220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,7 +510,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -548,7 +551,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -589,7 +592,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -630,7 +633,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -671,7 +674,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -712,7 +715,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -753,7 +756,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -794,7 +797,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -835,7 +838,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -876,7 +879,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -917,7 +920,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -958,7 +961,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -999,7 +1002,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1040,7 +1043,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1081,7 +1084,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1122,7 +1125,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1163,7 +1166,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1204,7 +1207,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1245,7 +1248,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1286,7 +1289,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1327,7 +1330,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1368,7 +1371,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -1409,7 +1412,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -1450,7 +1453,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -1491,7 +1494,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -1532,7 +1535,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -1573,7 +1576,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -1614,7 +1617,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -1696,7 +1699,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -1737,7 +1740,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -1778,7 +1781,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -1819,7 +1822,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -1860,7 +1863,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -1901,7 +1904,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -1942,7 +1945,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -1983,7 +1986,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -2024,7 +2027,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -2065,7 +2068,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -2106,7 +2109,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -2147,7 +2150,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -2188,7 +2191,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -2229,7 +2232,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -2270,7 +2273,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -2311,7 +2314,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -2352,7 +2355,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -2393,7 +2396,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -2434,7 +2437,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -2475,7 +2478,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -2516,7 +2519,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -2557,7 +2560,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -2598,7 +2601,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -2639,7 +2642,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -2680,7 +2683,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -2721,7 +2724,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -2762,7 +2765,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J57" t="n">
@@ -2803,7 +2806,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -2844,7 +2847,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -2885,7 +2888,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -2926,7 +2929,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -2967,7 +2970,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -3008,7 +3011,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -3049,7 +3052,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -3090,7 +3093,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -3131,7 +3134,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -3172,7 +3175,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -3213,7 +3216,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J68" t="n">
@@ -3254,7 +3257,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J69" t="n">
@@ -3295,7 +3298,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -3336,7 +3339,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -3377,7 +3380,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -3418,7 +3421,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -3459,7 +3462,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -3500,7 +3503,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -3541,7 +3544,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -3582,7 +3585,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -3623,7 +3626,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -3664,7 +3667,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -3705,7 +3708,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J80" t="n">
@@ -3746,7 +3749,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J81" t="n">
@@ -3787,7 +3790,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J82" t="n">
@@ -3828,7 +3831,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J83" t="n">
@@ -3869,7 +3872,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J84" t="n">
@@ -3910,7 +3913,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J85" t="n">
@@ -3951,7 +3954,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -3992,7 +3995,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J87" t="n">
@@ -4033,7 +4036,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J88" t="n">
@@ -4074,7 +4077,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -4115,7 +4118,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -4156,7 +4159,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J91" t="n">
@@ -4197,7 +4200,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -4238,7 +4241,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -4279,7 +4282,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -4320,7 +4323,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -4361,7 +4364,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -4402,7 +4405,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J97" t="n">
@@ -4443,7 +4446,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -4484,7 +4487,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -4525,7 +4528,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -4566,7 +4569,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -4607,7 +4610,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -4648,14 +4651,14 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="104">
@@ -4689,7 +4692,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J104" t="n">
@@ -4730,7 +4733,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J105" t="n">
@@ -4771,7 +4774,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -4812,7 +4815,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -4853,7 +4856,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -4894,7 +4897,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -4935,14 +4938,14 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J110" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K110" t="n">
-        <v>7.5</v>
+        <v>-32.5</v>
       </c>
     </row>
     <row r="111">
@@ -4976,7 +4979,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J111" t="n">
@@ -5017,7 +5020,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J112" t="n">
@@ -5058,7 +5061,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -5099,7 +5102,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -5140,7 +5143,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -5181,7 +5184,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -5222,7 +5225,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -5263,7 +5266,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -5304,7 +5307,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -5345,7 +5348,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -5386,7 +5389,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -5427,7 +5430,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J122" t="n">
@@ -5468,7 +5471,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J123" t="n">
@@ -5509,7 +5512,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J124" t="n">
@@ -5550,7 +5553,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -5591,7 +5594,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J126" t="n">
@@ -5632,7 +5635,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J127" t="n">
@@ -5673,7 +5676,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J128" t="n">
@@ -5714,7 +5717,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J129" t="n">
@@ -5755,7 +5758,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J130" t="n">
@@ -5796,7 +5799,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J131" t="n">
@@ -5837,7 +5840,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J132" t="n">
@@ -5878,7 +5881,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -5919,7 +5922,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -5960,7 +5963,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -6001,7 +6004,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J136" t="n">
@@ -6042,7 +6045,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -6083,7 +6086,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -6124,7 +6127,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -6165,7 +6168,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J140" t="n">
@@ -6206,7 +6209,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J141" t="n">
@@ -6247,7 +6250,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J142" t="n">
@@ -6288,7 +6291,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J143" t="n">
@@ -6329,7 +6332,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J144" t="n">
@@ -6370,7 +6373,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J145" t="n">
@@ -6411,7 +6414,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J146" t="n">
@@ -6452,7 +6455,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J147" t="n">
@@ -6493,7 +6496,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J148" t="n">
@@ -6534,7 +6537,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J149" t="n">
@@ -6575,7 +6578,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J150" t="n">
@@ -6616,7 +6619,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J151" t="n">
@@ -6657,7 +6660,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J152" t="n">
@@ -6698,7 +6701,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J153" t="n">
@@ -6739,7 +6742,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J154" t="n">
@@ -6780,7 +6783,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J155" t="n">
@@ -6821,7 +6824,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J156" t="n">
@@ -6862,7 +6865,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J157" t="n">
@@ -6903,7 +6906,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -6944,7 +6947,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -6985,7 +6988,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J160" t="n">
@@ -7026,7 +7029,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J161" t="n">
@@ -7067,7 +7070,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -7108,7 +7111,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -7149,7 +7152,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -7190,7 +7193,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -7231,7 +7234,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -7272,7 +7275,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -7313,7 +7316,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -7354,7 +7357,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -7395,7 +7398,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -7436,7 +7439,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J171" t="n">
@@ -7477,7 +7480,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J172" t="n">
@@ -7518,7 +7521,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J173" t="n">
@@ -7559,7 +7562,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J174" t="n">
@@ -7600,7 +7603,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J175" t="n">
@@ -7641,7 +7644,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J176" t="n">
@@ -7682,7 +7685,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J177" t="n">
@@ -7723,7 +7726,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J178" t="n">
@@ -7764,7 +7767,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J179" t="n">
@@ -7805,7 +7808,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J180" t="n">
@@ -7846,7 +7849,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J181" t="n">
@@ -7887,7 +7890,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J182" t="n">
@@ -7928,7 +7931,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J183" t="n">
@@ -7969,7 +7972,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J184" t="n">
@@ -8010,7 +8013,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J185" t="n">
@@ -8051,7 +8054,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J186" t="n">
@@ -8092,7 +8095,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J187" t="n">
@@ -8133,7 +8136,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J188" t="n">
@@ -8174,7 +8177,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J189" t="n">
@@ -8215,7 +8218,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J190" t="n">
@@ -8256,7 +8259,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J191" t="n">
@@ -8264,6 +8267,610 @@
       </c>
       <c r="K191" t="n">
         <v>7.75</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>BasicHours</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>MonFriOvertime</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>SatSunOvertime</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>AnnualHoliday</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>TotalPaidHours</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>A-EL CLNR</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" t="n">
+        <v>42.25</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>A-EL DPCH</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>7</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>A-EL PKNG HIGH_RISK</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" t="n">
+        <v>126.5</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>A-EL PKNG SLEEVING</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>37</v>
+      </c>
+      <c r="C197" t="n">
+        <v>0</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>A-EL PROD BELT</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>114</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>A-EL PROD FORMING</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" t="n">
+        <v>14.75</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>A-EL PROD FRYING</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" t="n">
+        <v>34.25</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>A-EL PROD PREPARATION</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>67.75</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" t="n">
+        <v>67.75</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>A-EL TECHNICAL</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0</v>
+      </c>
+      <c r="D202" t="n">
+        <v>0</v>
+      </c>
+      <c r="E202" t="n">
+        <v>0</v>
+      </c>
+      <c r="F202" t="n">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>A-PM PKNG HIGH_RISK</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" t="n">
+        <v>0</v>
+      </c>
+      <c r="F203" t="n">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>A-RS PKNG SLEEVING</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0</v>
+      </c>
+      <c r="E204" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" t="n">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>A-RS PROD BELT</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>7</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0</v>
+      </c>
+      <c r="E205" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>A-RS PROD FRYING</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>0</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0</v>
+      </c>
+      <c r="E206" t="n">
+        <v>0</v>
+      </c>
+      <c r="F206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>CLNR</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0</v>
+      </c>
+      <c r="D207" t="n">
+        <v>0</v>
+      </c>
+      <c r="E207" t="n">
+        <v>0</v>
+      </c>
+      <c r="F207" t="n">
+        <v>42.25</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>DPCH</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" t="n">
+        <v>11.25</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>OFCE</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" t="n">
+        <v>109.25</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>PKNG HIGH_RISK</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="C210" t="n">
+        <v>0</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0</v>
+      </c>
+      <c r="F210" t="n">
+        <v>88.5</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>PKNG SLEEVING</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="C211" t="n">
+        <v>0</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" t="n">
+        <v>79.75</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>PROD BELT</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="C212" t="n">
+        <v>0</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+      <c r="F212" t="n">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>PROD FORMING</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="C213" t="n">
+        <v>0</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0</v>
+      </c>
+      <c r="E213" t="n">
+        <v>0</v>
+      </c>
+      <c r="F213" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>PROD FRYING</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>48</v>
+      </c>
+      <c r="C214" t="n">
+        <v>0</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0</v>
+      </c>
+      <c r="E214" t="n">
+        <v>0</v>
+      </c>
+      <c r="F214" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>PROD PREPARATION</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" t="n">
+        <v>100.5</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>PROD TABLE</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>51</v>
+      </c>
+      <c r="C216" t="n">
+        <v>0</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0</v>
+      </c>
+      <c r="E216" t="n">
+        <v>0</v>
+      </c>
+      <c r="F216" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>TECH TECHNICAL</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>41</v>
+      </c>
+      <c r="C217" t="n">
+        <v>0</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" t="n">
+        <v>0</v>
+      </c>
+      <c r="F217" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>WRHS</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="C218" t="n">
+        <v>0</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0</v>
+      </c>
+      <c r="F218" t="n">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Grand total</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>1213.25</v>
+      </c>
+      <c r="C220" t="n">
+        <v>0</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" t="n">
+        <v>1213.25</v>
       </c>
     </row>
   </sheetData>
@@ -8368,7 +8975,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -8409,7 +9016,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -8450,7 +9057,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -8491,7 +9098,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -8532,7 +9139,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -8573,7 +9180,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -8614,7 +9221,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -8655,7 +9262,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -8696,7 +9303,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -8737,7 +9344,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -8778,7 +9385,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -8819,7 +9426,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -8860,7 +9467,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -8901,7 +9508,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -8942,7 +9549,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -8983,7 +9590,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -9024,7 +9631,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -9065,7 +9672,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -9106,7 +9713,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -9147,7 +9754,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -9188,7 +9795,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -9229,7 +9836,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -9270,7 +9877,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -9311,7 +9918,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -9352,7 +9959,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -9393,7 +10000,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -9434,7 +10041,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -9475,7 +10082,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -9557,7 +10164,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -9598,7 +10205,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -9639,7 +10246,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -9680,7 +10287,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -9721,7 +10328,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -9762,7 +10369,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -9803,7 +10410,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -9844,7 +10451,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -9885,7 +10492,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -9926,7 +10533,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -9967,7 +10574,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -10008,7 +10615,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -10049,7 +10656,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -10090,7 +10697,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -10131,7 +10738,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -10172,7 +10779,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -10213,7 +10820,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -10254,7 +10861,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -10295,7 +10902,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -10336,7 +10943,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -10377,7 +10984,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -10418,7 +11025,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -10459,7 +11066,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -10500,7 +11107,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -10541,7 +11148,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -10582,7 +11189,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -10623,7 +11230,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J57" t="n">
@@ -10664,7 +11271,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -10705,7 +11312,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -10746,7 +11353,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -10787,7 +11394,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -10828,7 +11435,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -10869,7 +11476,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -10910,7 +11517,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -10951,7 +11558,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -10992,7 +11599,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -11033,7 +11640,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -11074,7 +11681,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J68" t="n">
@@ -11115,7 +11722,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J69" t="n">
@@ -11156,7 +11763,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -11197,7 +11804,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -11238,7 +11845,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -11279,7 +11886,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -11320,7 +11927,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -11361,7 +11968,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -11402,7 +12009,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -11443,7 +12050,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -11484,7 +12091,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -11525,7 +12132,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -11566,7 +12173,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J80" t="n">
@@ -11607,7 +12214,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J81" t="n">
@@ -11648,7 +12255,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J82" t="n">
@@ -11689,7 +12296,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J83" t="n">
@@ -11730,7 +12337,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J84" t="n">
@@ -11771,7 +12378,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J85" t="n">
@@ -11812,7 +12419,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -11853,7 +12460,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J87" t="n">
@@ -11894,7 +12501,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J88" t="n">
@@ -11935,7 +12542,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -11976,7 +12583,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -12017,7 +12624,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J91" t="n">
@@ -12058,7 +12665,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -12170,7 +12777,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -12211,7 +12818,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -12252,7 +12859,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -12293,7 +12900,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -12334,7 +12941,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -12375,7 +12982,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -12416,7 +13023,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -12457,7 +13064,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -12498,7 +13105,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -12539,7 +13146,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -12580,14 +13187,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="13">
@@ -12621,7 +13228,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -12662,7 +13269,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -12703,7 +13310,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -12744,7 +13351,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -12785,7 +13392,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -12826,7 +13433,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -12867,14 +13474,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K19" t="n">
-        <v>7.5</v>
+        <v>-32.5</v>
       </c>
     </row>
     <row r="20">
@@ -12908,7 +13515,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -12949,7 +13556,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -12990,7 +13597,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -13031,7 +13638,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -13072,7 +13679,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -13113,7 +13720,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -13154,7 +13761,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -13195,7 +13802,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -13236,7 +13843,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -13277,7 +13884,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -13318,7 +13925,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -13359,7 +13966,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -13400,7 +14007,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -13441,7 +14048,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -13482,7 +14089,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -13523,7 +14130,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -13564,7 +14171,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -13605,7 +14212,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -13646,7 +14253,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -13687,7 +14294,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -13728,7 +14335,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -13769,7 +14376,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -13810,7 +14417,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -13851,7 +14458,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -13892,7 +14499,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -13933,7 +14540,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -13974,7 +14581,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -14015,7 +14622,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -14056,7 +14663,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -14097,7 +14704,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -14138,7 +14745,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -14179,7 +14786,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -14220,7 +14827,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -14261,7 +14868,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -14302,7 +14909,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -14343,7 +14950,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -14384,7 +14991,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -14425,7 +15032,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J57" t="n">
@@ -14466,7 +15073,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -14507,7 +15114,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -14548,7 +15155,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -14589,7 +15196,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -14630,7 +15237,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -14671,7 +15278,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -14712,7 +15319,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -14753,7 +15360,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -14794,7 +15401,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -14835,7 +15442,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -14876,7 +15483,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J68" t="n">
@@ -14917,7 +15524,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J69" t="n">
@@ -14958,7 +15565,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -14999,7 +15606,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -15040,7 +15647,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -15081,7 +15688,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -15122,7 +15729,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -15163,7 +15770,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -15204,7 +15811,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -15245,7 +15852,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -15286,7 +15893,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -15327,7 +15934,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -15368,7 +15975,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J80" t="n">
@@ -15409,7 +16016,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J81" t="n">
@@ -15450,7 +16057,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J82" t="n">
@@ -15491,7 +16098,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J83" t="n">
@@ -15532,7 +16139,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J84" t="n">
@@ -15573,7 +16180,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J85" t="n">
@@ -15614,7 +16221,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -15655,7 +16262,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J87" t="n">
@@ -15696,7 +16303,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J88" t="n">
@@ -15737,7 +16344,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -15778,7 +16385,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -15819,7 +16426,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J91" t="n">
@@ -15860,7 +16467,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -15901,7 +16508,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -15942,7 +16549,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -15983,7 +16590,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -16024,7 +16631,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -16065,7 +16672,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J97" t="n">
@@ -16106,7 +16713,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -16147,7 +16754,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -16188,7 +16795,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -16209,7 +16816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16794,6 +17401,809 @@
         <v>34.5</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Grand total</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1213.25</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1213.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>BasicHours</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>MonFriOvertime</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SatSunOvertime</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>AnnualHoliday</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>TotalPaidHours</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>740</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AGENCY</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>473.25</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>473.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1213.25</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1213.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Basic Hour</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Mon Fri O</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Sat Sun O</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Annual Ho</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Total Paid Hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A-EL CLNR</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A-EL DPCH</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A-EL PKNG HIGH_RISK</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>126.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A-EL PKNG SLEEVING</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>37</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A-EL PROD BELT</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>114</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A-EL PROD FORMING</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>14.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A-EL PROD FRYING</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>34.25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A-EL PROD PREPARATION</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>67.75</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>67.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A-EL TECHNICAL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A-PM PKNG HIGH_RISK</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A-RS PKNG SLEEVING</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A-RS PROD BELT</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A-RS PROD FRYING</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CLNR</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>42.25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DPCH</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>11.25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>OFCE</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>109.25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PKNG HIGH_RISK</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>88.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PKNG SLEEVING</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>79.75</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PROD BELT</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PROD FORMING</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PROD FRYING</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>48</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PROD PREPARATION</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>100.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PROD TABLE</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>51</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TECH TECHNICAL</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>41</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>WRHS</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Grand total</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1213.25</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1213.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>SageNo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>TotalPaidHours</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>BasicHours</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Overtime</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ContractedHours</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
